--- a/DateBase/orders/Dang Nguyen48_2026-7-5.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-5.xlsx
@@ -517,6 +517,9 @@
       <c r="A11" t="str">
         <v>2</v>
       </c>
+      <c r="C11" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-7-5.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-5.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -520,10 +520,96 @@
       <c r="C11" t="str">
         <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>188_戴安娜_Diana_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3</v>
+      </c>
+      <c r="C17" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>173_朱丽叶_Juliet_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -578,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010155201010550</v>
+        <v>01010155201010551010108410912830</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-5.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-5.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -606,10 +606,93 @@
       <c r="C21" t="str">
         <v>173_朱丽叶_Juliet_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>890_康乃馨红绸_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>4</v>
+      </c>
+      <c r="C24" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F27" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +747,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010155201010551010108410912830</v>
+        <v>010101552010105510101084109128381031081015107100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-5.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-5.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -689,10 +689,75 @@
       <c r="A31" t="str">
         <v>5</v>
       </c>
+      <c r="C31" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F31" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>44_拉丝粉_Spider Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>610_康乃馨黄_yellow_undefined_20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>6</v>
+      </c>
+      <c r="C34" t="str">
+        <v>726_鸢尾叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>790_铁线莲粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L38"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -747,7 +812,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010101552010105510101084109128381031081015107100</v>
+        <v>01010155201010551010108410912838103108101510710208.55102051010</v>
       </c>
     </row>
   </sheetData>
